--- a/contact_forms/044_service_advisor_follow_up_form--contact_forms.xlsx
+++ b/contact_forms/044_service_advisor_follow_up_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Would you like to book a service advisor follow up call?</t>
+          <t>Would you like to book a service advisor follow-up call?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your preferred contact method?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What is your contact information?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Would you like to be contacted via Email?</t>
+          <t>Would you like to be contacted via Phone/Email?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Would you like to be contacted via Text/SMS?</t>
+          <t>Additional comments?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your contact phone number?</t>
+          <t>Contact Information?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is your contact email address?</t>
+          <t>Service Advisor Follow Up Form Page 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,241 +847,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Would you like to be contacted via Phone?</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What is your contact email address?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Would you like to be contacted via Email?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What is your contact phone number?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Would you like to be contacted via Phone?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Would you like to be contacted via Text/SMS?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your contact phone number?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your contact email address?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Would you like to be contacted via Email?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your contact phone number?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is your contact email address?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'service_issue'}</t>
+          <t>service_issue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Service issue'}</t>
+          <t>Service issue</t>
         </is>
       </c>
     </row>
@@ -1148,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'consultation'}</t>
+          <t>consultation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Consultation'}</t>
+          <t>Consultation</t>
         </is>
       </c>
     </row>
@@ -1165,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1199,29 +969,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_4_choices</t>
+          <t>service_advisor_follow_up_form_page_7_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1003,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_7_choices</t>
+          <t>service_advisor_follow_up_form_page_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1267,267 +1037,182 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_8_choices</t>
+          <t>service_advisor_follow_up_form_page_9_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_11_choices</t>
+          <t>service_advisor_follow_up_form_page_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_11_choices</t>
+          <t>service_advisor_follow_up_form_page_9_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_12_choices</t>
+          <t>service_advisor_follow_up_form_page_10_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Phone Number</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_12_choices</t>
+          <t>service_advisor_follow_up_form_page_10_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Email Address</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_15_choices</t>
+          <t>service_advisor_follow_up_form_page_11_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>yes_-_phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Yes - Phone</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_15_choices</t>
+          <t>service_advisor_follow_up_form_page_11_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>yes_-_email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Yes - Email</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_17_choices</t>
+          <t>service_advisor_follow_up_form_page_11_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_17_choices</t>
+          <t>service_advisor_follow_up_form_page_13_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Phone Number</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>service_advisor_follow_up_form_page_19_choices</t>
+          <t>service_advisor_follow_up_form_page_13_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>service_advisor_follow_up_form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
+          <t>Email Address</t>
         </is>
       </c>
     </row>
